--- a/XLSX/VVK_EIR_s3_NSIK_11.10_LER.xlsx
+++ b/XLSX/VVK_EIR_s3_NSIK_11.10_LER.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="LoIN" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="LOI" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="94">
   <si>
     <t xml:space="preserve">Komponento pavadinimas pagal NSIK klasifikatorių</t>
   </si>
@@ -64,14 +64,16 @@
     <t xml:space="preserve">Statinio kodas - ClassificationSystem.NSIK E arba „NSIK E“ klasifikatorius</t>
   </si>
   <si>
-    <t xml:space="preserve">TP modeliai 
-LOD, LoG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atributas arba 
+    <t xml:space="preserve">TP modeliai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavadinimas arba 
 Savybių rinkinys.Pavadinimas</t>
   </si>
   <si>
+    <t xml:space="preserve">Nuoroda</t>
+  </si>
+  <si>
     <t xml:space="preserve">Atributo ar savybės aprašymas</t>
   </si>
   <si>
@@ -93,7 +95,7 @@
     <t xml:space="preserve">Šulinys</t>
   </si>
   <si>
-    <t xml:space="preserve">%M10</t>
+    <t xml:space="preserve">M</t>
   </si>
   <si>
     <t xml:space="preserve">HJ</t>
@@ -105,12 +107,12 @@
     <t xml:space="preserve">Uždara kamera, skirta srauto jungtims ar kitoms svarbioms vietoms po žeme.</t>
   </si>
   <si>
-    <t xml:space="preserve">Apžiūros šulinys, 
-kamera, 
+    <t xml:space="preserve">inspektavimo šulinys, 
+perkritimo šulinys, 
 komunikacijų šulinys, 
 valymo šulinys, 
-inspektavimo šulinys, 
-perkritimo šulinys</t>
+kamera, 
+Apžiūros šulinys</t>
   </si>
   <si>
     <t xml:space="preserve">IfcFlowTerminal, 
@@ -118,9 +120,6 @@
 IfcFlowTerminalElementTypeEnum</t>
   </si>
   <si>
-    <t xml:space="preserve">LoG 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">LER</t>
   </si>
   <si>
@@ -130,25 +129,113 @@
     <t xml:space="preserve">Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
   </si>
   <si>
-    <t xml:space="preserve">String</t>
+    <t xml:space="preserve">Tekstas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The building service system that requires the provision for voids, e.g. 'Air Conditioning', 'Plumbing', 'Electro', etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pset_ElementComponentCommon.Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the allowed values for selection of the flow meter operation type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The tag (or label) identifier at the particular instance of a product, e.g. the serial number, or the position number. It is the identifier at the occurrence level.</t>
   </si>
   <si>
     <t xml:space="preserve">Pset_ConstructionAdministration.SpecificationSectionNumber</t>
   </si>
   <si>
+    <t xml:space="preserve">SpecificationSectionNumber</t>
+  </si>
+  <si>
     <t xml:space="preserve">A reference number to an external contract technical specification section describing either (a) minimum performance requirements of a given IfcProductType/[[IfcProduct]] or (b) a preselection for a specific IfcProductType/[[IfcProduct]] made for this project.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pset_ElementComponentCommon.Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defines the allowed values for selection of the flow meter operation type.</t>
+    <t xml:space="preserve">VVK.Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pset_QuantityTakeOff.Heigth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pset_QuantityTakeOff.Width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The width of the object. Only given, if the object has constant thickness (prismatic).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skaičius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pset_QuantityTakeOff.Length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The length of the object.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ženklas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nekintančią, statišką informaciją ant vaizduojantis komponentas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parkavimo ženklas, 
+įspėjamasis ženklas, 
+nuoroda, 
+Sargelis, 
+gaisrinės saugos ženklinimas, 
+lentelė, 
+reklaminis ženklas, 
+Avarinis ženklas, 
+Informacinis ženklas, 
+kelio ženklas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IfcPlate, 
+IfcPlateType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VVK.Finish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[Description]] of the (surface) finish of the object for informational purposes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VVK.Colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[Colour]] of this object.</t>
   </si>
   <si>
     <t xml:space="preserve">Stulpas</t>
@@ -157,18 +244,15 @@
     <t xml:space="preserve">UBD</t>
   </si>
   <si>
-    <t xml:space="preserve">Tinklo informacinio ženklo laikiklis</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vertikalus komponentas, daugiausia veikiamas vertikaliai žemyn nukreiptų gniuždymo jėgų. Skirtas laikyti kitą objektą fiksuotoje vertikalioje padėtyje.</t>
   </si>
   <si>
-    <t xml:space="preserve">elektros bokštas, 
+    <t xml:space="preserve">stulpas, 
+elektros bokštas, 
+Sargelio stovas, 
+Informacinio ženklo stovas, 
+Atraminis laikiklis, 
 stiebas, 
-stulpas, 
-Informacinio ženklo stovas, 
-Sargelio stovas, 
-Atraminis laikiklis, 
 elektros pilonas</t>
   </si>
   <si>
@@ -176,13 +260,68 @@
 IfcColumnType</t>
   </si>
   <si>
+    <t xml:space="preserve">Kolona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiesios ar kreivos linijos formos konstrukcinis laikantis komponentas, daugiausia perduodantis gniuždymo jėgas kitiems konstrukciniams objektams.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">viaduko kolona, 
+Pamatas, 
+gniuždoma komponentas, 
+Balustra, 
+stulpas, 
+kompozitinė kolona, 
+tauras, 
+tilto kolona, 
+gniuždomas elementas, 
+montuojama kolona, 
+betonuojama kolona, 
+tilto pilonas, 
+kolona pamatas, 
+tilto tarpinė atrama, 
+užbetonuotas vamzdis, 
+statramstis, 
+monolitinė kolona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IfcPile, 
+IfcPileType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duomenų kabelis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WGB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektrinio signalo nukreipimo komponentas, skirtas duomenų perdavimui.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duomenų šyna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IfcFlowSegment, 
+IfcFlowSegmentType, 
+IfcFlowSegmentTypeEnum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pset_QuantityTakeOff.Diameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The [[Diameter]] of the object.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Įrangos ir (ar) kabelių dėklas</t>
   </si>
   <si>
     <t xml:space="preserve">UBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duomenų kabelio dėklas</t>
   </si>
   <si>
     <t xml:space="preserve">Tarp fiksuotų padėčių objektą ar objektus palaikantis komponentas, kuris įrengtas išilgai laikomojo komponento ar sistemos ir yra nuolatiniame sąlytyje su tuo komponentu ar sistema.</t>
@@ -208,64 +347,6 @@
 įrenginių dėklas</t>
   </si>
   <si>
-    <t xml:space="preserve">IfcFlowSegment, 
-IfcFlowSegmentType, 
-IfcFlowSegmentTypeEnum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signalo kabelio lizdas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryšių įrangos lizdas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elektrinių signalų jungiamasis komponentas vienam kištukiniam sujungimui.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signalų kabelio lizdas, 
-signalų kabelio kištukinis lizdas, 
- signalinis lizdas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IfcEquipmentElement, 
-IfcDistributionElement, 
-IfcDistributionElementType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korpusas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korpusas (skydelis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaubtas, skirtas mechanizmams ar jų dalims apsaugoti nuo išorinio poveikio bei užtikrinti žmonių saugumą (taip pat ir nuo kontakto su elektros srove).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">montavimo dėžė, 
-spintelė, 
-paskirstymo skydelis, 
-saugos dėžutė, 
-Ryšių spinta, 
-skydinė, 
-sensorių dėžutė, 
-Centralė, 
-prietaisų dėžė, 
-Ryšių skydelis, 
-kolektorių spintelė, 
-elektros spinta, 
-elektros skydelis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IfcJunctionBox, 
-IfcJunctionBoxType</t>
-  </si>
-  <si>
     <t xml:space="preserve">DCB</t>
   </si>
   <si>
@@ -279,16 +360,10 @@
     <t xml:space="preserve">Pset_QuantityTakeOff.Area</t>
   </si>
   <si>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calculated area for the object.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pset_QuantityTakeOff.Width</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The width of the object. Only given, if the object has constant thickness (prismatic).</t>
   </si>
 </sst>
 </file>
@@ -298,7 +373,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,12 +403,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Wingdings 2"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Verdana"/>
       <family val="0"/>
@@ -354,18 +423,12 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEEDE5"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -376,7 +439,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFFEEDE5"/>
+        <bgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
   </fills>
@@ -431,7 +494,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="29">
+  <cellStyleXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -460,34 +523,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -497,19 +548,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -521,23 +572,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -558,22 +609,19 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="15">
+  <cellStyles count="12">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="VVK2_centered" xfId="20"/>
-    <cellStyle name="VVK2_check" xfId="21"/>
-    <cellStyle name="VVK2_container" xfId="22"/>
-    <cellStyle name="VVK2_head" xfId="23"/>
-    <cellStyle name="VVK2_headV" xfId="24"/>
-    <cellStyle name="VVK2_lod" xfId="25"/>
-    <cellStyle name="VVK2_properties" xfId="26"/>
-    <cellStyle name="VVK2_right" xfId="27"/>
-    <cellStyle name="VVK2_title" xfId="28"/>
+    <cellStyle name="VVK_centered" xfId="20"/>
+    <cellStyle name="VVK_container" xfId="21"/>
+    <cellStyle name="VVK_head" xfId="22"/>
+    <cellStyle name="VVK_headV" xfId="23"/>
+    <cellStyle name="VVK_properties" xfId="24"/>
+    <cellStyle name="VVK_title" xfId="25"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -595,7 +643,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFEEDE5"/>
+      <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -818,23 +866,26 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T1048576"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
+  <dimension ref="A1:V1048576"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="27.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="32.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="14.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -863,21 +914,22 @@
       <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="124.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="139.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -899,71 +951,76 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="V2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="M3" s="2" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+    <row r="4" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>28</v>
       </c>
+      <c r="J4" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="K4" s="6"/>
-      <c r="L4" s="8" t="s">
-        <v>29</v>
-      </c>
+      <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
@@ -971,11 +1028,13 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
-      <c r="T4" s="9" t="s">
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="5" customFormat="false" ht="49.15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -987,19 +1046,22 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="6"/>
+      <c r="N5" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="O5" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="P5" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T5" s="9"/>
-    </row>
-    <row r="6" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="R5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="31.75" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1011,19 +1073,22 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="6"/>
+      <c r="N6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="O6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="R6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V6" s="9"/>
+    </row>
+    <row r="7" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A7" s="4"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1035,19 +1100,22 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="6"/>
+      <c r="N7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="O7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="P7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="P7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A8" s="4"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1059,19 +1127,22 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" s="11" t="s">
+      <c r="M8" s="6"/>
+      <c r="N8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="P8" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="O8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="R8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V8" s="9"/>
+    </row>
+    <row r="9" customFormat="false" ht="40.45" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1083,52 +1154,49 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="T9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="M9" s="6"/>
+      <c r="N9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="7" t="s">
+      <c r="O9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="P9" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="R9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V9" s="9"/>
+    </row>
+    <row r="10" customFormat="false" ht="75.3" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="O10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="P10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="R10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V10" s="9"/>
+    </row>
+    <row r="11" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1140,19 +1208,13 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N11" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M11" s="6"/>
+      <c r="N11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="V11" s="9"/>
+    </row>
+    <row r="12" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1164,19 +1226,13 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M12" s="6"/>
+      <c r="N12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="V12" s="9"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1188,19 +1244,22 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="P13" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M13" s="6"/>
+      <c r="N13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="R13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V13" s="9"/>
+    </row>
+    <row r="14" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1212,19 +1271,22 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N14" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="P14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M14" s="6"/>
+      <c r="N14" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="R14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V14" s="9"/>
+    </row>
+    <row r="15" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1236,40 +1298,38 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="T15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="M15" s="6"/>
+      <c r="V15" s="9"/>
+    </row>
+    <row r="16" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="K16" s="6"/>
-      <c r="L16" s="8" t="s">
-        <v>29</v>
-      </c>
+      <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
@@ -1277,11 +1337,13 @@
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
-      <c r="T16" s="9" t="s">
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+    <row r="17" customFormat="false" ht="49.15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1293,19 +1355,22 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="10" t="s">
+      <c r="M17" s="6"/>
+      <c r="N17" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="N17" s="11" t="s">
+      <c r="O17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P17" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="P17" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="R17" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V17" s="9"/>
+    </row>
+    <row r="18" customFormat="false" ht="31.75" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1317,19 +1382,22 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="10" t="s">
+      <c r="M18" s="6"/>
+      <c r="N18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="N18" s="11" t="s">
+      <c r="O18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="P18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P18" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T18" s="9"/>
-    </row>
-    <row r="19" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="R18" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V18" s="9"/>
+    </row>
+    <row r="19" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1341,19 +1409,22 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="10" t="s">
+      <c r="M19" s="6"/>
+      <c r="N19" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N19" s="11" t="s">
+      <c r="O19" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="P19" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T19" s="9"/>
-    </row>
-    <row r="20" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="P19" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="R19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V19" s="9"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1365,19 +1436,22 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N20" s="11" t="s">
+      <c r="M20" s="6"/>
+      <c r="N20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="P20" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T20" s="9"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="O20" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P20" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="R20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V20" s="9"/>
+    </row>
+    <row r="21" customFormat="false" ht="40.45" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1389,52 +1463,49 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="T21" s="9"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="K22" s="6"/>
-      <c r="L22" s="8" t="s">
-        <v>29</v>
-      </c>
+      <c r="M21" s="6"/>
+      <c r="N21" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="P21" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="R21" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V21" s="9"/>
+    </row>
+    <row r="22" customFormat="false" ht="75.3" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
       <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="N22" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="P22" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="R22" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V22" s="9"/>
+    </row>
+    <row r="23" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1446,19 +1517,13 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="P23" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T23" s="9"/>
-    </row>
-    <row r="24" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M23" s="6"/>
+      <c r="N23" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="V23" s="9"/>
+    </row>
+    <row r="24" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1470,19 +1535,13 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="N24" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="P24" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T24" s="9"/>
-    </row>
-    <row r="25" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M24" s="6"/>
+      <c r="N24" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="V24" s="9"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1494,19 +1553,22 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="P25" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T25" s="9"/>
-    </row>
-    <row r="26" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M25" s="6"/>
+      <c r="N25" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P25" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="R25" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V25" s="9"/>
+    </row>
+    <row r="26" customFormat="false" ht="20.85" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1518,19 +1580,22 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N26" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="P26" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T26" s="9"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M26" s="6"/>
+      <c r="N26" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="P26" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="R26" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V26" s="9"/>
+    </row>
+    <row r="27" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1542,52 +1607,49 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="T27" s="9"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7" t="s">
+      <c r="M27" s="6"/>
+      <c r="N27" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="O27" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="P27" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="J28" s="7" t="s">
+      <c r="R27" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V27" s="9"/>
+    </row>
+    <row r="28" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="K28" s="6"/>
-      <c r="L28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="O28" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="P28" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="R28" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V28" s="9"/>
+    </row>
+    <row r="29" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A29" s="4"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1599,43 +1661,52 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N29" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="P29" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T29" s="9"/>
-    </row>
-    <row r="30" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="N30" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="P30" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T30" s="9"/>
-    </row>
-    <row r="31" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M29" s="6"/>
+      <c r="V29" s="9"/>
+    </row>
+    <row r="30" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="V30" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="49.15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A31" s="4"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -1647,19 +1718,22 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="N31" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="P31" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T31" s="9"/>
-    </row>
-    <row r="32" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M31" s="6"/>
+      <c r="N31" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O31" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V31" s="9"/>
+    </row>
+    <row r="32" customFormat="false" ht="31.75" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A32" s="4"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -1671,19 +1745,22 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N32" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="P32" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T32" s="9"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="M32" s="6"/>
+      <c r="N32" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="P32" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V32" s="9"/>
+    </row>
+    <row r="33" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A33" s="4"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -1695,47 +1772,50 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="T33" s="9"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
-      <c r="A34" s="12"/>
-      <c r="B34" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="K34" s="6"/>
-      <c r="L34" s="8" t="s">
-        <v>29</v>
-      </c>
+      <c r="M33" s="6"/>
+      <c r="N33" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O33" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="P33" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="R33" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V33" s="9"/>
+    </row>
+    <row r="34" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
       <c r="M34" s="6"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A35" s="12"/>
+      <c r="N34" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="O34" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P34" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="R34" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V34" s="9"/>
+    </row>
+    <row r="35" customFormat="false" ht="40.45" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A35" s="4"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -1746,20 +1826,23 @@
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="N35" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="P35" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T35" s="9"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A36" s="12"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="O35" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="P35" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="R35" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V35" s="9"/>
+    </row>
+    <row r="36" customFormat="false" ht="75.3" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A36" s="4"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -1770,20 +1853,23 @@
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="N36" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="P36" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="T36" s="9"/>
-    </row>
-    <row r="37" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A37" s="12"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="O36" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="P36" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="R36" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V36" s="9"/>
+    </row>
+    <row r="37" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A37" s="4"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -1794,20 +1880,14 @@
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N37" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="P37" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="T37" s="9"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A38" s="12"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="V37" s="9"/>
+    </row>
+    <row r="38" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A38" s="4"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -1818,48 +1898,1155 @@
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="T38" s="9"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14"/>
-      <c r="O39" s="14"/>
-      <c r="P39" s="14"/>
-      <c r="Q39" s="14"/>
-      <c r="R39" s="14"/>
-      <c r="S39" s="14"/>
-      <c r="T39" s="15"/>
-    </row>
-    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="V38" s="9"/>
+    </row>
+    <row r="39" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="O39" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="R39" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V39" s="9"/>
+    </row>
+    <row r="40" customFormat="false" ht="20.85" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="O40" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="P40" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="R40" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V40" s="9"/>
+    </row>
+    <row r="41" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="P41" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R41" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V41" s="9"/>
+    </row>
+    <row r="42" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="O42" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="P42" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="R42" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V42" s="9"/>
+    </row>
+    <row r="43" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A43" s="4"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="M43" s="6"/>
+      <c r="V43" s="9"/>
+    </row>
+    <row r="44" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
+      <c r="V44" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="49.15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O45" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R45" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V45" s="9"/>
+    </row>
+    <row r="46" customFormat="false" ht="31.75" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O46" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="P46" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R46" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V46" s="9"/>
+    </row>
+    <row r="47" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O47" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="R47" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V47" s="9"/>
+    </row>
+    <row r="48" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="O48" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P48" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="R48" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V48" s="9"/>
+    </row>
+    <row r="49" customFormat="false" ht="40.45" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="O49" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="R49" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V49" s="9"/>
+    </row>
+    <row r="50" customFormat="false" ht="75.3" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="O50" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="P50" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="R50" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V50" s="9"/>
+    </row>
+    <row r="51" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="V51" s="9"/>
+    </row>
+    <row r="52" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A52" s="4"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="V52" s="9"/>
+    </row>
+    <row r="53" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A53" s="4"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="O53" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="R53" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V53" s="9"/>
+    </row>
+    <row r="54" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="O54" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="R54" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V54" s="9"/>
+    </row>
+    <row r="55" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A55" s="4"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="M55" s="6"/>
+      <c r="V55" s="9"/>
+    </row>
+    <row r="56" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6"/>
+      <c r="T56" s="6"/>
+      <c r="U56" s="6"/>
+      <c r="V56" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="49.15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A57" s="4"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O57" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R57" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V57" s="9"/>
+    </row>
+    <row r="58" customFormat="false" ht="31.75" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A58" s="4"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O58" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R58" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V58" s="9"/>
+    </row>
+    <row r="59" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A59" s="4"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O59" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="P59" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="R59" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V59" s="9"/>
+    </row>
+    <row r="60" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A60" s="4"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="O60" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P60" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="R60" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V60" s="9"/>
+    </row>
+    <row r="61" customFormat="false" ht="75.3" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A61" s="4"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="O61" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="R61" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V61" s="9"/>
+    </row>
+    <row r="62" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A62" s="4"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="V62" s="9"/>
+    </row>
+    <row r="63" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A63" s="4"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="O63" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P63" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="R63" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V63" s="9"/>
+    </row>
+    <row r="64" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A64" s="4"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="O64" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="P64" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="R64" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V64" s="9"/>
+    </row>
+    <row r="65" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A65" s="4"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="M65" s="6"/>
+      <c r="V65" s="9"/>
+    </row>
+    <row r="66" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
+      <c r="U66" s="6"/>
+      <c r="V66" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="49.15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A67" s="4"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O67" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R67" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V67" s="9"/>
+    </row>
+    <row r="68" customFormat="false" ht="31.75" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A68" s="4"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O68" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="P68" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R68" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V68" s="9"/>
+    </row>
+    <row r="69" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A69" s="4"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O69" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="P69" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="R69" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V69" s="9"/>
+    </row>
+    <row r="70" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A70" s="4"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="O70" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P70" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="R70" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V70" s="9"/>
+    </row>
+    <row r="71" customFormat="false" ht="75.3" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A71" s="4"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="O71" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="P71" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="R71" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V71" s="9"/>
+    </row>
+    <row r="72" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="V72" s="9"/>
+    </row>
+    <row r="73" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A73" s="4"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="O73" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="R73" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V73" s="9"/>
+    </row>
+    <row r="74" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="O74" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="P74" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="R74" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V74" s="9"/>
+    </row>
+    <row r="75" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A75" s="4"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="M75" s="6"/>
+      <c r="V75" s="9"/>
+    </row>
+    <row r="76" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A76" s="12"/>
+      <c r="B76" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" s="6"/>
+      <c r="E76" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F76" s="6"/>
+      <c r="G76" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
+      <c r="O76" s="6"/>
+      <c r="P76" s="6"/>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="6"/>
+      <c r="U76" s="6"/>
+      <c r="V76" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="31.75" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A77" s="12"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O77" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="P77" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R77" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V77" s="9"/>
+    </row>
+    <row r="78" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A78" s="12"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O78" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="P78" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="R78" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V78" s="9"/>
+    </row>
+    <row r="79" customFormat="false" ht="23.05" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A79" s="12"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="O79" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P79" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="R79" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V79" s="9"/>
+    </row>
+    <row r="80" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A80" s="12"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="O80" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="P80" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="R80" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="V80" s="9"/>
+    </row>
+    <row r="81" customFormat="false" ht="5.65" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
+      <c r="A81" s="12"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="5"/>
+      <c r="M81" s="6"/>
+      <c r="V81" s="9"/>
+    </row>
+    <row r="82" customFormat="false" ht="20.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="13"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="14"/>
+      <c r="L82" s="14"/>
+      <c r="M82" s="14"/>
+      <c r="N82" s="14"/>
+      <c r="O82" s="14"/>
+      <c r="P82" s="14"/>
+      <c r="Q82" s="14"/>
+      <c r="R82" s="14"/>
+      <c r="S82" s="14"/>
+      <c r="T82" s="14"/>
+      <c r="U82" s="14"/>
+      <c r="V82" s="15"/>
+    </row>
     <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1878,7 +3065,7 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="87">
+  <mergeCells count="101">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:G2"/>
@@ -1886,111 +3073,156 @@
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:S1"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="E4:E9"/>
-    <mergeCell ref="F4:F9"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="H4:H9"/>
-    <mergeCell ref="I4:I9"/>
-    <mergeCell ref="J4:J9"/>
-    <mergeCell ref="K4:K9"/>
-    <mergeCell ref="L4:L9"/>
-    <mergeCell ref="T4:T9"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="C10:C15"/>
-    <mergeCell ref="D10:D15"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="F10:F15"/>
-    <mergeCell ref="G10:G15"/>
-    <mergeCell ref="H10:H15"/>
-    <mergeCell ref="I10:I15"/>
-    <mergeCell ref="J10:J15"/>
-    <mergeCell ref="K10:K15"/>
-    <mergeCell ref="L10:L15"/>
-    <mergeCell ref="T10:T15"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="G16:G21"/>
-    <mergeCell ref="H16:H21"/>
-    <mergeCell ref="I16:I21"/>
-    <mergeCell ref="J16:J21"/>
-    <mergeCell ref="K16:K21"/>
-    <mergeCell ref="L16:L21"/>
-    <mergeCell ref="T16:T21"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="D22:D27"/>
-    <mergeCell ref="E22:E27"/>
-    <mergeCell ref="F22:F27"/>
-    <mergeCell ref="G22:G27"/>
-    <mergeCell ref="H22:H27"/>
-    <mergeCell ref="I22:I27"/>
-    <mergeCell ref="J22:J27"/>
-    <mergeCell ref="K22:K27"/>
-    <mergeCell ref="L22:L27"/>
-    <mergeCell ref="T22:T27"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="C28:C33"/>
-    <mergeCell ref="D28:D33"/>
-    <mergeCell ref="E28:E33"/>
-    <mergeCell ref="F28:F33"/>
-    <mergeCell ref="G28:G33"/>
-    <mergeCell ref="H28:H33"/>
-    <mergeCell ref="I28:I33"/>
-    <mergeCell ref="J28:J33"/>
-    <mergeCell ref="K28:K33"/>
-    <mergeCell ref="L28:L33"/>
-    <mergeCell ref="T28:T33"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="E34:E38"/>
-    <mergeCell ref="F34:F38"/>
-    <mergeCell ref="G34:G38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="I34:I38"/>
-    <mergeCell ref="J34:J38"/>
-    <mergeCell ref="K34:K38"/>
-    <mergeCell ref="L34:L38"/>
-    <mergeCell ref="T34:T38"/>
+    <mergeCell ref="M1:U1"/>
+    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:A15"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="C4:C15"/>
+    <mergeCell ref="D4:D15"/>
+    <mergeCell ref="E4:E15"/>
+    <mergeCell ref="F4:F15"/>
+    <mergeCell ref="G4:G15"/>
+    <mergeCell ref="H4:H15"/>
+    <mergeCell ref="I4:I15"/>
+    <mergeCell ref="J4:J15"/>
+    <mergeCell ref="K4:K15"/>
+    <mergeCell ref="M4:M15"/>
+    <mergeCell ref="V4:V15"/>
+    <mergeCell ref="A16:A29"/>
+    <mergeCell ref="B16:B29"/>
+    <mergeCell ref="C16:C29"/>
+    <mergeCell ref="D16:D29"/>
+    <mergeCell ref="E16:E29"/>
+    <mergeCell ref="F16:F29"/>
+    <mergeCell ref="G16:G29"/>
+    <mergeCell ref="H16:H29"/>
+    <mergeCell ref="I16:I29"/>
+    <mergeCell ref="J16:J29"/>
+    <mergeCell ref="K16:K29"/>
+    <mergeCell ref="M16:M29"/>
+    <mergeCell ref="V16:V29"/>
+    <mergeCell ref="A30:A43"/>
+    <mergeCell ref="B30:B43"/>
+    <mergeCell ref="C30:C43"/>
+    <mergeCell ref="D30:D43"/>
+    <mergeCell ref="E30:E43"/>
+    <mergeCell ref="F30:F43"/>
+    <mergeCell ref="G30:G43"/>
+    <mergeCell ref="H30:H43"/>
+    <mergeCell ref="I30:I43"/>
+    <mergeCell ref="J30:J43"/>
+    <mergeCell ref="K30:K43"/>
+    <mergeCell ref="M30:M43"/>
+    <mergeCell ref="V30:V43"/>
+    <mergeCell ref="A44:A55"/>
+    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="C44:C55"/>
+    <mergeCell ref="D44:D55"/>
+    <mergeCell ref="E44:E55"/>
+    <mergeCell ref="F44:F55"/>
+    <mergeCell ref="G44:G55"/>
+    <mergeCell ref="H44:H55"/>
+    <mergeCell ref="I44:I55"/>
+    <mergeCell ref="J44:J55"/>
+    <mergeCell ref="K44:K55"/>
+    <mergeCell ref="M44:M55"/>
+    <mergeCell ref="V44:V55"/>
+    <mergeCell ref="A56:A65"/>
+    <mergeCell ref="B56:B65"/>
+    <mergeCell ref="C56:C65"/>
+    <mergeCell ref="D56:D65"/>
+    <mergeCell ref="E56:E65"/>
+    <mergeCell ref="F56:F65"/>
+    <mergeCell ref="G56:G65"/>
+    <mergeCell ref="H56:H65"/>
+    <mergeCell ref="I56:I65"/>
+    <mergeCell ref="J56:J65"/>
+    <mergeCell ref="K56:K65"/>
+    <mergeCell ref="M56:M65"/>
+    <mergeCell ref="V56:V65"/>
+    <mergeCell ref="A66:A75"/>
+    <mergeCell ref="B66:B75"/>
+    <mergeCell ref="C66:C75"/>
+    <mergeCell ref="D66:D75"/>
+    <mergeCell ref="E66:E75"/>
+    <mergeCell ref="F66:F75"/>
+    <mergeCell ref="G66:G75"/>
+    <mergeCell ref="H66:H75"/>
+    <mergeCell ref="I66:I75"/>
+    <mergeCell ref="J66:J75"/>
+    <mergeCell ref="K66:K75"/>
+    <mergeCell ref="M66:M75"/>
+    <mergeCell ref="V66:V75"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="B76:B81"/>
+    <mergeCell ref="C76:C81"/>
+    <mergeCell ref="D76:D81"/>
+    <mergeCell ref="E76:E81"/>
+    <mergeCell ref="F76:F81"/>
+    <mergeCell ref="G76:G81"/>
+    <mergeCell ref="H76:H81"/>
+    <mergeCell ref="I76:I81"/>
+    <mergeCell ref="J76:J81"/>
+    <mergeCell ref="K76:K81"/>
+    <mergeCell ref="M76:M81"/>
+    <mergeCell ref="V76:V81"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="M5" r:id="rId1" display="Name"/>
-    <hyperlink ref="M6" r:id="rId2" display="Pset_ConstructionAdministration.SpecificationSectionNumber"/>
-    <hyperlink ref="M7" r:id="rId3" display="Pset_ElementComponentCommon.Status"/>
-    <hyperlink ref="M8" r:id="rId4" display="Type"/>
-    <hyperlink ref="M11" r:id="rId5" display="Name"/>
-    <hyperlink ref="M12" r:id="rId6" display="Pset_ConstructionAdministration.SpecificationSectionNumber"/>
-    <hyperlink ref="M13" r:id="rId7" display="Pset_ElementComponentCommon.Status"/>
-    <hyperlink ref="M14" r:id="rId8" display="Type"/>
-    <hyperlink ref="M17" r:id="rId9" display="Name"/>
-    <hyperlink ref="M18" r:id="rId10" display="Pset_ConstructionAdministration.SpecificationSectionNumber"/>
-    <hyperlink ref="M19" r:id="rId11" display="Pset_ElementComponentCommon.Status"/>
-    <hyperlink ref="M20" r:id="rId12" display="Type"/>
-    <hyperlink ref="M23" r:id="rId13" display="Name"/>
-    <hyperlink ref="M24" r:id="rId14" display="Pset_ConstructionAdministration.SpecificationSectionNumber"/>
-    <hyperlink ref="M25" r:id="rId15" display="Pset_ElementComponentCommon.Status"/>
-    <hyperlink ref="M26" r:id="rId16" display="Type"/>
-    <hyperlink ref="M29" r:id="rId17" display="Name"/>
-    <hyperlink ref="M30" r:id="rId18" display="Pset_ConstructionAdministration.SpecificationSectionNumber"/>
-    <hyperlink ref="M31" r:id="rId19" display="Pset_ElementComponentCommon.Status"/>
-    <hyperlink ref="M32" r:id="rId20" display="Type"/>
-    <hyperlink ref="M35" r:id="rId21" display="Pset_ElementComponentCommon.Status"/>
-    <hyperlink ref="M36" r:id="rId22" display="Pset_QuantityTakeOff.Area"/>
-    <hyperlink ref="M37" r:id="rId23" display="Pset_QuantityTakeOff.Width"/>
+    <hyperlink ref="O5" r:id="rId1" display="Name"/>
+    <hyperlink ref="O6" r:id="rId2" display="System"/>
+    <hyperlink ref="O7" r:id="rId3" display="Status"/>
+    <hyperlink ref="O8" r:id="rId4" display="Type"/>
+    <hyperlink ref="O9" r:id="rId5" display="Tag"/>
+    <hyperlink ref="O10" r:id="rId6" display="SpecificationSectionNumber"/>
+    <hyperlink ref="O13" r:id="rId7" display="Width"/>
+    <hyperlink ref="O14" r:id="rId8" display="Length"/>
+    <hyperlink ref="O17" r:id="rId9" display="Name"/>
+    <hyperlink ref="O18" r:id="rId10" display="System"/>
+    <hyperlink ref="O19" r:id="rId11" display="Status"/>
+    <hyperlink ref="O20" r:id="rId12" display="Type"/>
+    <hyperlink ref="O21" r:id="rId13" display="Tag"/>
+    <hyperlink ref="O22" r:id="rId14" display="SpecificationSectionNumber"/>
+    <hyperlink ref="O25" r:id="rId15" display="Width"/>
+    <hyperlink ref="O26" r:id="rId16" display="Length"/>
+    <hyperlink ref="O27" r:id="rId17" display="Finish"/>
+    <hyperlink ref="O28" r:id="rId18" display="Colour"/>
+    <hyperlink ref="O31" r:id="rId19" display="Name"/>
+    <hyperlink ref="O32" r:id="rId20" display="System"/>
+    <hyperlink ref="O33" r:id="rId21" display="Status"/>
+    <hyperlink ref="O34" r:id="rId22" display="Type"/>
+    <hyperlink ref="O35" r:id="rId23" display="Tag"/>
+    <hyperlink ref="O36" r:id="rId24" display="SpecificationSectionNumber"/>
+    <hyperlink ref="O39" r:id="rId25" display="Width"/>
+    <hyperlink ref="O40" r:id="rId26" display="Length"/>
+    <hyperlink ref="O41" r:id="rId27" display="Finish"/>
+    <hyperlink ref="O42" r:id="rId28" display="Colour"/>
+    <hyperlink ref="O45" r:id="rId29" display="Name"/>
+    <hyperlink ref="O46" r:id="rId30" display="System"/>
+    <hyperlink ref="O47" r:id="rId31" display="Status"/>
+    <hyperlink ref="O48" r:id="rId32" display="Type"/>
+    <hyperlink ref="O49" r:id="rId33" display="Tag"/>
+    <hyperlink ref="O50" r:id="rId34" display="SpecificationSectionNumber"/>
+    <hyperlink ref="O53" r:id="rId35" display="Width"/>
+    <hyperlink ref="O54" r:id="rId36" display="Length"/>
+    <hyperlink ref="O57" r:id="rId37" display="Name"/>
+    <hyperlink ref="O58" r:id="rId38" display="System"/>
+    <hyperlink ref="O59" r:id="rId39" display="Status"/>
+    <hyperlink ref="O60" r:id="rId40" display="Type"/>
+    <hyperlink ref="O61" r:id="rId41" display="SpecificationSectionNumber"/>
+    <hyperlink ref="O63" r:id="rId42" display="Diameter"/>
+    <hyperlink ref="O64" r:id="rId43" display="Length"/>
+    <hyperlink ref="O67" r:id="rId44" display="Name"/>
+    <hyperlink ref="O68" r:id="rId45" display="System"/>
+    <hyperlink ref="O69" r:id="rId46" display="Status"/>
+    <hyperlink ref="O70" r:id="rId47" display="Type"/>
+    <hyperlink ref="O71" r:id="rId48" display="SpecificationSectionNumber"/>
+    <hyperlink ref="O73" r:id="rId49" display="Diameter"/>
+    <hyperlink ref="O74" r:id="rId50" display="Length"/>
+    <hyperlink ref="O77" r:id="rId51" display="System"/>
+    <hyperlink ref="O78" r:id="rId52" display="Status"/>
+    <hyperlink ref="O79" r:id="rId53" display="Width"/>
+    <hyperlink ref="O80" r:id="rId54" display="Area"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2306,13 +3538,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10686352-4E78-4563-858C-3C148132DADB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{592B4AEE-E38F-4ACF-AE41-15DDCD69589D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1629C07-BAB6-465F-87DB-24782C35BA2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F827859-B672-4D4D-A053-C9A85C0CB4C0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3FEEEC9-14F6-417F-BCD2-2166693D6B1D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33439299-B384-4E13-8CDA-5972538431EF}"/>
 </file>